--- a/results/Int All Data -1.0/Rando_8_permute.xlsx
+++ b/results/Int All Data -1.0/Rando_8_permute.xlsx
@@ -440,367 +440,367 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.719908000404854</v>
+        <v>0.7236232344349319</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7207367296866221</v>
+        <v>0.7245322365045738</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7172654551292567</v>
+        <v>0.7277293620407437</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.717817941317102</v>
+        <v>0.725164995480293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7167129689414113</v>
+        <v>0.72931073596186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7187248493140166</v>
+        <v>0.7285226665922107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7174677076534868</v>
+        <v>0.731325757443556</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7010609968484205</v>
+        <v>0.7312069188162905</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7000352502242403</v>
+        <v>0.7313268044799196</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.701535304321119</v>
+        <v>0.7318396777920098</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.701535304321119</v>
+        <v>0.7324317768556102</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7024828722301526</v>
+        <v>0.7303792365708861</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7002718804424077</v>
+        <v>0.7280900660679945</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6997579600939541</v>
+        <v>0.6971956876062306</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7032698945634381</v>
+        <v>0.7028790009877043</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.703072877221026</v>
+        <v>0.7012236364968956</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7072561365056209</v>
+        <v>0.6985008184334242</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7046104501209327</v>
+        <v>0.6919105970550357</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7029529915573968</v>
+        <v>0.6919105970550357</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7031896217755642</v>
+        <v>0.6919105970550357</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7067015562450485</v>
+        <v>0.6916739668368683</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7176355824837797</v>
+        <v>0.6915551282096026</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7179514384534575</v>
+        <v>0.69127888511568</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7163637823141598</v>
+        <v>0.69127888511568</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7053067293027087</v>
+        <v>0.69127888511568</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7019511522635181</v>
+        <v>0.7027215965210472</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7019511522635181</v>
+        <v>0.7065879527996007</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6916519790732332</v>
+        <v>0.7016145300726294</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6925641222519658</v>
+        <v>0.7006263022514772</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6897620784369841</v>
+        <v>0.7006263022514772</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.68865605902493</v>
+        <v>0.7094608460751842</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.69303424157921</v>
+        <v>0.7014435141332458</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6889281139733983</v>
+        <v>0.6854224617220956</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6853338126433131</v>
+        <v>0.6875531807219665</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6831228208555683</v>
+        <v>0.6894087036642782</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6690803181594497</v>
+        <v>0.6890907536218733</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6570151436359384</v>
+        <v>0.6941423550639914</v>
       </c>
     </row>
     <row r="39">
@@ -810,587 +810,587 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6522793981634982</v>
+        <v>0.6965107513183932</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6229121222380054</v>
+        <v>0.6882536480491968</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6098421418175853</v>
+        <v>0.688450665391609</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6039201041452169</v>
+        <v>0.6870308840826043</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6066001682238424</v>
+        <v>0.6870308840826043</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5950688077396928</v>
+        <v>0.7023483280574334</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5863072074493147</v>
+        <v>0.7002957877727094</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.584962463746366</v>
+        <v>0.6885726451279652</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5567741507662561</v>
+        <v>0.6968192780335261</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5576028800480241</v>
+        <v>0.6979638632849718</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5573266369541015</v>
+        <v>0.6987529796909846</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5596501851509303</v>
+        <v>0.6990688356606625</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5558599135147964</v>
+        <v>0.704950213420912</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5532538400058634</v>
+        <v>0.7058988283663092</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5491498064727788</v>
+        <v>0.7046739703269894</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5571222903571441</v>
+        <v>0.7017541349211058</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5615432268962701</v>
+        <v>0.6975698286001473</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5832788292737408</v>
+        <v>0.6910150319520596</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5776330346952949</v>
+        <v>0.6762584504559843</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5776330346952949</v>
+        <v>0.6699840850472737</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5815400508859673</v>
+        <v>0.6722722085138018</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5714368480017311</v>
+        <v>0.6639035958718846</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5620456298447245</v>
+        <v>0.6646541464385058</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5684002680413091</v>
+        <v>0.6745259542863924</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5653959717020972</v>
+        <v>0.6825380510465129</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5695010522715453</v>
+        <v>0.6825380510465129</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5593509072570091</v>
+        <v>0.674719830519714</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5709927300775156</v>
+        <v>0.6742465700833791</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5650268913839378</v>
+        <v>0.6733386150501006</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5621445747810822</v>
+        <v>0.6754265800651257</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5577152619510475</v>
+        <v>0.6747187834833503</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5359191059705504</v>
+        <v>0.6753504954227061</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.524391933631855</v>
+        <v>0.6720741441350258</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5266383501499007</v>
+        <v>0.6632697898598018</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5228887384258856</v>
+        <v>0.6703374598199796</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5213501184896152</v>
+        <v>0.6179825005322435</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5294007810891272</v>
+        <v>0.6034208423058532</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5273075808922844</v>
+        <v>0.579674406592141</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5323195694586473</v>
+        <v>0.5917123581701993</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.527931963577095</v>
+        <v>0.5909679153156989</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5331399224495067</v>
+        <v>0.5806645539799598</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5217649193956506</v>
+        <v>0.5873620965856144</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5198676895048565</v>
+        <v>0.5873620965856144</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5162744352111349</v>
+        <v>0.5852261424039257</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5097185915266838</v>
+        <v>0.5275881866377219</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5106661594357172</v>
+        <v>0.5237176422137141</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5101564272327178</v>
+        <v>0.5243504011894333</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5092880850751946</v>
+        <v>0.5300368556799978</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5048587722451601</v>
+        <v>0.5247515906227423</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5029625893907296</v>
+        <v>0.5267687061771655</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.504621094990629</v>
+        <v>0.5352624396645296</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5047409806542581</v>
+        <v>0.5197448372381973</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5055697099360261</v>
+        <v>0.5060431448784216</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5057667272784384</v>
+        <v>0.5063193879723443</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5057667272784384</v>
+        <v>0.5060035320026665</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5057667272784384</v>
+        <v>0.5115407838114218</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5048181123330413</v>
+        <v>0.5053081253511935</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5026092146180237</v>
+        <v>0.5056239813208713</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5018982769271577</v>
+        <v>0.5173825486959163</v>
       </c>
     </row>
     <row r="98">
@@ -1400,543 +1400,543 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5018982769271577</v>
+        <v>0.5173825486959163</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5028458448361911</v>
+        <v>0.5168654872383718</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.504503303399727</v>
+        <v>0.5182060427958662</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.504503303399727</v>
+        <v>0.5201845925108979</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5038715914603714</v>
+        <v>0.5181695710292018</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5075430244692398</v>
+        <v>0.5134755325052439</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5107411970417732</v>
+        <v>0.5124893987568189</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5104253410720954</v>
+        <v>0.5199052083078846</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5097550632933482</v>
+        <v>0.5191546577412633</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5115699263235413</v>
+        <v>0.5164307926414284</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5106223584145078</v>
+        <v>0.5164704055171836</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5105827455387526</v>
+        <v>0.512959518084063</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5108986015084304</v>
+        <v>0.516356802071736</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5099114207236417</v>
+        <v>0.5120922229629035</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5106619712902629</v>
+        <v>0.5127239349022592</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5077400418116521</v>
+        <v>0.50968526086911</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5075430244692398</v>
+        <v>0.5111477961629607</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5082143492843506</v>
+        <v>0.5101210025024169</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5082143492843506</v>
+        <v>0.4929991658610304</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5081361705692039</v>
+        <v>0.50324406766647</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5034765097391832</v>
+        <v>0.5036381023512947</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5034765097391832</v>
+        <v>0.5052173821996838</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5032388324846522</v>
+        <v>0.5030063904119391</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5048577252087965</v>
+        <v>0.4987845652879525</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5087678825085595</v>
+        <v>0.497836997378919</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5119264422053378</v>
+        <v>0.4977202528243806</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5138215780234048</v>
+        <v>0.4977202528243806</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5106630183266265</v>
+        <v>0.4958647298820688</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5035943013300852</v>
+        <v>0.4957479853275304</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5035943013300852</v>
+        <v>0.4877775955158922</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5035943013300852</v>
+        <v>0.4877775955158922</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.4872636751674386</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.4875795311371164</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5</v>
+        <v>0.4895111387218478</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.4919973265671517</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.492549812754997</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.4943615346760993</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>0.4943604876397357</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5</v>
+        <v>0.4970040799516967</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5</v>
+        <v>0.4963327551365859</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5</v>
+        <v>0.4974773403880317</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.4964505467274878</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.4923861260701584</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.4938851331306736</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.4949108797548539</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.4949108797548539</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.4949108797548539</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.4997268980151681</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.4997268980151681</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.4969623730032144</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.4973178418486474</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.4949504926306091</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.4979485067516395</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.5000792257515103</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B156" t="n">
